--- a/Elnet/Results_Production_Elnet_xgb.xlsx
+++ b/Elnet/Results_Production_Elnet_xgb.xlsx
@@ -28,511 +28,511 @@
     <t>Lookup</t>
   </si>
   <si>
-    <t>19.08.202614</t>
-  </si>
-  <si>
-    <t>19.08.202615</t>
-  </si>
-  <si>
-    <t>19.08.202616</t>
-  </si>
-  <si>
-    <t>19.08.202617</t>
-  </si>
-  <si>
-    <t>19.08.202618</t>
-  </si>
-  <si>
-    <t>19.08.202619</t>
-  </si>
-  <si>
-    <t>19.08.202620</t>
-  </si>
-  <si>
-    <t>19.08.202621</t>
-  </si>
-  <si>
-    <t>19.08.202622</t>
-  </si>
-  <si>
-    <t>19.08.202623</t>
-  </si>
-  <si>
-    <t>19.08.202624</t>
-  </si>
-  <si>
-    <t>20.08.20261</t>
-  </si>
-  <si>
-    <t>20.08.20262</t>
-  </si>
-  <si>
-    <t>20.08.20263</t>
-  </si>
-  <si>
-    <t>20.08.20264</t>
-  </si>
-  <si>
-    <t>20.08.20265</t>
-  </si>
-  <si>
-    <t>20.08.20266</t>
-  </si>
-  <si>
-    <t>20.08.20267</t>
-  </si>
-  <si>
-    <t>20.08.20268</t>
-  </si>
-  <si>
-    <t>20.08.20269</t>
-  </si>
-  <si>
-    <t>20.08.202610</t>
-  </si>
-  <si>
-    <t>20.08.202611</t>
-  </si>
-  <si>
-    <t>20.08.202612</t>
-  </si>
-  <si>
-    <t>20.08.202613</t>
-  </si>
-  <si>
-    <t>20.08.202614</t>
-  </si>
-  <si>
-    <t>20.08.202615</t>
-  </si>
-  <si>
-    <t>20.08.202616</t>
-  </si>
-  <si>
-    <t>20.08.202617</t>
-  </si>
-  <si>
-    <t>20.08.202618</t>
-  </si>
-  <si>
-    <t>20.08.202619</t>
-  </si>
-  <si>
-    <t>20.08.202620</t>
-  </si>
-  <si>
-    <t>20.08.202621</t>
-  </si>
-  <si>
-    <t>20.08.202622</t>
-  </si>
-  <si>
-    <t>20.08.202623</t>
-  </si>
-  <si>
-    <t>20.08.202624</t>
-  </si>
-  <si>
-    <t>21.08.20261</t>
-  </si>
-  <si>
-    <t>21.08.20262</t>
-  </si>
-  <si>
-    <t>21.08.20263</t>
-  </si>
-  <si>
-    <t>21.08.20264</t>
-  </si>
-  <si>
-    <t>21.08.20265</t>
-  </si>
-  <si>
-    <t>21.08.20266</t>
-  </si>
-  <si>
-    <t>21.08.20267</t>
-  </si>
-  <si>
-    <t>21.08.20268</t>
-  </si>
-  <si>
-    <t>21.08.20269</t>
-  </si>
-  <si>
-    <t>21.08.202610</t>
-  </si>
-  <si>
-    <t>21.08.202611</t>
-  </si>
-  <si>
-    <t>21.08.202612</t>
-  </si>
-  <si>
-    <t>21.08.202613</t>
-  </si>
-  <si>
-    <t>21.08.202614</t>
-  </si>
-  <si>
-    <t>21.08.202615</t>
-  </si>
-  <si>
-    <t>21.08.202616</t>
-  </si>
-  <si>
-    <t>21.08.202617</t>
-  </si>
-  <si>
-    <t>21.08.202618</t>
-  </si>
-  <si>
-    <t>21.08.202619</t>
-  </si>
-  <si>
-    <t>21.08.202620</t>
-  </si>
-  <si>
-    <t>21.08.202621</t>
-  </si>
-  <si>
-    <t>21.08.202622</t>
-  </si>
-  <si>
-    <t>21.08.202623</t>
-  </si>
-  <si>
-    <t>21.08.202624</t>
-  </si>
-  <si>
-    <t>22.08.20261</t>
-  </si>
-  <si>
-    <t>22.08.20262</t>
-  </si>
-  <si>
-    <t>22.08.20263</t>
-  </si>
-  <si>
-    <t>22.08.20264</t>
-  </si>
-  <si>
-    <t>22.08.20265</t>
-  </si>
-  <si>
-    <t>22.08.20266</t>
-  </si>
-  <si>
-    <t>22.08.20267</t>
-  </si>
-  <si>
-    <t>22.08.20268</t>
-  </si>
-  <si>
-    <t>22.08.20269</t>
-  </si>
-  <si>
-    <t>22.08.202610</t>
-  </si>
-  <si>
-    <t>22.08.202611</t>
-  </si>
-  <si>
-    <t>22.08.202612</t>
-  </si>
-  <si>
-    <t>22.08.202613</t>
-  </si>
-  <si>
-    <t>22.08.202614</t>
-  </si>
-  <si>
-    <t>22.08.202615</t>
-  </si>
-  <si>
-    <t>22.08.202616</t>
-  </si>
-  <si>
-    <t>22.08.202617</t>
-  </si>
-  <si>
-    <t>22.08.202618</t>
-  </si>
-  <si>
-    <t>22.08.202619</t>
-  </si>
-  <si>
-    <t>22.08.202620</t>
-  </si>
-  <si>
-    <t>22.08.202621</t>
-  </si>
-  <si>
-    <t>22.08.202622</t>
-  </si>
-  <si>
-    <t>22.08.202623</t>
-  </si>
-  <si>
-    <t>22.08.202624</t>
-  </si>
-  <si>
-    <t>23.08.20261</t>
-  </si>
-  <si>
-    <t>23.08.20262</t>
-  </si>
-  <si>
-    <t>23.08.20263</t>
-  </si>
-  <si>
-    <t>23.08.20264</t>
-  </si>
-  <si>
-    <t>23.08.20265</t>
-  </si>
-  <si>
-    <t>23.08.20266</t>
-  </si>
-  <si>
-    <t>23.08.20267</t>
-  </si>
-  <si>
-    <t>23.08.20268</t>
-  </si>
-  <si>
-    <t>23.08.20269</t>
-  </si>
-  <si>
-    <t>23.08.202610</t>
-  </si>
-  <si>
-    <t>23.08.202611</t>
-  </si>
-  <si>
-    <t>23.08.202612</t>
-  </si>
-  <si>
-    <t>23.08.202613</t>
-  </si>
-  <si>
-    <t>23.08.202614</t>
-  </si>
-  <si>
-    <t>23.08.202615</t>
-  </si>
-  <si>
-    <t>23.08.202616</t>
-  </si>
-  <si>
-    <t>23.08.202617</t>
-  </si>
-  <si>
-    <t>23.08.202618</t>
-  </si>
-  <si>
-    <t>23.08.202619</t>
-  </si>
-  <si>
-    <t>23.08.202620</t>
-  </si>
-  <si>
-    <t>23.08.202621</t>
-  </si>
-  <si>
-    <t>23.08.202622</t>
-  </si>
-  <si>
-    <t>23.08.202623</t>
-  </si>
-  <si>
-    <t>23.08.202624</t>
-  </si>
-  <si>
-    <t>24.08.20261</t>
-  </si>
-  <si>
-    <t>24.08.20262</t>
-  </si>
-  <si>
-    <t>24.08.20263</t>
-  </si>
-  <si>
-    <t>24.08.20264</t>
-  </si>
-  <si>
-    <t>24.08.20265</t>
-  </si>
-  <si>
-    <t>24.08.20266</t>
-  </si>
-  <si>
-    <t>24.08.20267</t>
-  </si>
-  <si>
-    <t>24.08.20268</t>
-  </si>
-  <si>
-    <t>24.08.20269</t>
-  </si>
-  <si>
-    <t>24.08.202610</t>
-  </si>
-  <si>
-    <t>24.08.202611</t>
-  </si>
-  <si>
-    <t>24.08.202612</t>
-  </si>
-  <si>
-    <t>24.08.202613</t>
-  </si>
-  <si>
-    <t>24.08.202614</t>
-  </si>
-  <si>
-    <t>24.08.202615</t>
-  </si>
-  <si>
-    <t>24.08.202616</t>
-  </si>
-  <si>
-    <t>24.08.202617</t>
-  </si>
-  <si>
-    <t>24.08.202618</t>
-  </si>
-  <si>
-    <t>24.08.202619</t>
-  </si>
-  <si>
-    <t>24.08.202620</t>
-  </si>
-  <si>
-    <t>24.08.202621</t>
-  </si>
-  <si>
-    <t>24.08.202622</t>
-  </si>
-  <si>
-    <t>24.08.202623</t>
-  </si>
-  <si>
-    <t>24.08.202624</t>
-  </si>
-  <si>
-    <t>25.08.20261</t>
-  </si>
-  <si>
-    <t>25.08.20262</t>
-  </si>
-  <si>
-    <t>25.08.20263</t>
-  </si>
-  <si>
-    <t>25.08.20264</t>
-  </si>
-  <si>
-    <t>25.08.20265</t>
-  </si>
-  <si>
-    <t>25.08.20266</t>
-  </si>
-  <si>
-    <t>25.08.20267</t>
-  </si>
-  <si>
-    <t>25.08.20268</t>
-  </si>
-  <si>
-    <t>25.08.20269</t>
-  </si>
-  <si>
-    <t>25.08.202610</t>
-  </si>
-  <si>
-    <t>25.08.202611</t>
-  </si>
-  <si>
-    <t>25.08.202612</t>
-  </si>
-  <si>
-    <t>25.08.202613</t>
-  </si>
-  <si>
-    <t>25.08.202614</t>
-  </si>
-  <si>
-    <t>25.08.202615</t>
-  </si>
-  <si>
-    <t>25.08.202616</t>
-  </si>
-  <si>
-    <t>25.08.202617</t>
-  </si>
-  <si>
-    <t>25.08.202618</t>
-  </si>
-  <si>
-    <t>25.08.202619</t>
-  </si>
-  <si>
-    <t>25.08.202620</t>
-  </si>
-  <si>
-    <t>25.08.202621</t>
-  </si>
-  <si>
-    <t>25.08.202622</t>
-  </si>
-  <si>
-    <t>25.08.202623</t>
-  </si>
-  <si>
-    <t>25.08.202624</t>
-  </si>
-  <si>
-    <t>26.08.20261</t>
-  </si>
-  <si>
-    <t>26.08.20262</t>
-  </si>
-  <si>
-    <t>26.08.20263</t>
-  </si>
-  <si>
-    <t>26.08.20264</t>
-  </si>
-  <si>
-    <t>26.08.20265</t>
-  </si>
-  <si>
-    <t>26.08.20266</t>
-  </si>
-  <si>
-    <t>26.08.20267</t>
-  </si>
-  <si>
-    <t>26.08.20268</t>
-  </si>
-  <si>
-    <t>26.08.20269</t>
-  </si>
-  <si>
-    <t>26.08.202610</t>
-  </si>
-  <si>
-    <t>26.08.202611</t>
-  </si>
-  <si>
-    <t>26.08.202612</t>
-  </si>
-  <si>
-    <t>26.08.202613</t>
-  </si>
-  <si>
-    <t>26.08.202614</t>
+    <t>10.09.202614</t>
+  </si>
+  <si>
+    <t>10.09.202615</t>
+  </si>
+  <si>
+    <t>10.09.202616</t>
+  </si>
+  <si>
+    <t>10.09.202617</t>
+  </si>
+  <si>
+    <t>10.09.202618</t>
+  </si>
+  <si>
+    <t>10.09.202619</t>
+  </si>
+  <si>
+    <t>10.09.202620</t>
+  </si>
+  <si>
+    <t>10.09.202621</t>
+  </si>
+  <si>
+    <t>10.09.202622</t>
+  </si>
+  <si>
+    <t>10.09.202623</t>
+  </si>
+  <si>
+    <t>10.09.202624</t>
+  </si>
+  <si>
+    <t>11.09.20261</t>
+  </si>
+  <si>
+    <t>11.09.20262</t>
+  </si>
+  <si>
+    <t>11.09.20263</t>
+  </si>
+  <si>
+    <t>11.09.20264</t>
+  </si>
+  <si>
+    <t>11.09.20265</t>
+  </si>
+  <si>
+    <t>11.09.20266</t>
+  </si>
+  <si>
+    <t>11.09.20267</t>
+  </si>
+  <si>
+    <t>11.09.20268</t>
+  </si>
+  <si>
+    <t>11.09.20269</t>
+  </si>
+  <si>
+    <t>11.09.202610</t>
+  </si>
+  <si>
+    <t>11.09.202611</t>
+  </si>
+  <si>
+    <t>11.09.202612</t>
+  </si>
+  <si>
+    <t>11.09.202613</t>
+  </si>
+  <si>
+    <t>11.09.202614</t>
+  </si>
+  <si>
+    <t>11.09.202615</t>
+  </si>
+  <si>
+    <t>11.09.202616</t>
+  </si>
+  <si>
+    <t>11.09.202617</t>
+  </si>
+  <si>
+    <t>11.09.202618</t>
+  </si>
+  <si>
+    <t>11.09.202619</t>
+  </si>
+  <si>
+    <t>11.09.202620</t>
+  </si>
+  <si>
+    <t>11.09.202621</t>
+  </si>
+  <si>
+    <t>11.09.202622</t>
+  </si>
+  <si>
+    <t>11.09.202623</t>
+  </si>
+  <si>
+    <t>11.09.202624</t>
+  </si>
+  <si>
+    <t>12.09.20261</t>
+  </si>
+  <si>
+    <t>12.09.20262</t>
+  </si>
+  <si>
+    <t>12.09.20263</t>
+  </si>
+  <si>
+    <t>12.09.20264</t>
+  </si>
+  <si>
+    <t>12.09.20265</t>
+  </si>
+  <si>
+    <t>12.09.20266</t>
+  </si>
+  <si>
+    <t>12.09.20267</t>
+  </si>
+  <si>
+    <t>12.09.20268</t>
+  </si>
+  <si>
+    <t>12.09.20269</t>
+  </si>
+  <si>
+    <t>12.09.202610</t>
+  </si>
+  <si>
+    <t>12.09.202611</t>
+  </si>
+  <si>
+    <t>12.09.202612</t>
+  </si>
+  <si>
+    <t>12.09.202613</t>
+  </si>
+  <si>
+    <t>12.09.202614</t>
+  </si>
+  <si>
+    <t>12.09.202615</t>
+  </si>
+  <si>
+    <t>12.09.202616</t>
+  </si>
+  <si>
+    <t>12.09.202617</t>
+  </si>
+  <si>
+    <t>12.09.202618</t>
+  </si>
+  <si>
+    <t>12.09.202619</t>
+  </si>
+  <si>
+    <t>12.09.202620</t>
+  </si>
+  <si>
+    <t>12.09.202621</t>
+  </si>
+  <si>
+    <t>12.09.202622</t>
+  </si>
+  <si>
+    <t>12.09.202623</t>
+  </si>
+  <si>
+    <t>12.09.202624</t>
+  </si>
+  <si>
+    <t>13.09.20261</t>
+  </si>
+  <si>
+    <t>13.09.20262</t>
+  </si>
+  <si>
+    <t>13.09.20263</t>
+  </si>
+  <si>
+    <t>13.09.20264</t>
+  </si>
+  <si>
+    <t>13.09.20265</t>
+  </si>
+  <si>
+    <t>13.09.20266</t>
+  </si>
+  <si>
+    <t>13.09.20267</t>
+  </si>
+  <si>
+    <t>13.09.20268</t>
+  </si>
+  <si>
+    <t>13.09.20269</t>
+  </si>
+  <si>
+    <t>13.09.202610</t>
+  </si>
+  <si>
+    <t>13.09.202611</t>
+  </si>
+  <si>
+    <t>13.09.202612</t>
+  </si>
+  <si>
+    <t>13.09.202613</t>
+  </si>
+  <si>
+    <t>13.09.202614</t>
+  </si>
+  <si>
+    <t>13.09.202615</t>
+  </si>
+  <si>
+    <t>13.09.202616</t>
+  </si>
+  <si>
+    <t>13.09.202617</t>
+  </si>
+  <si>
+    <t>13.09.202618</t>
+  </si>
+  <si>
+    <t>13.09.202619</t>
+  </si>
+  <si>
+    <t>13.09.202620</t>
+  </si>
+  <si>
+    <t>13.09.202621</t>
+  </si>
+  <si>
+    <t>13.09.202622</t>
+  </si>
+  <si>
+    <t>13.09.202623</t>
+  </si>
+  <si>
+    <t>13.09.202624</t>
+  </si>
+  <si>
+    <t>14.09.20261</t>
+  </si>
+  <si>
+    <t>14.09.20262</t>
+  </si>
+  <si>
+    <t>14.09.20263</t>
+  </si>
+  <si>
+    <t>14.09.20264</t>
+  </si>
+  <si>
+    <t>14.09.20265</t>
+  </si>
+  <si>
+    <t>14.09.20266</t>
+  </si>
+  <si>
+    <t>14.09.20267</t>
+  </si>
+  <si>
+    <t>14.09.20268</t>
+  </si>
+  <si>
+    <t>14.09.20269</t>
+  </si>
+  <si>
+    <t>14.09.202610</t>
+  </si>
+  <si>
+    <t>14.09.202611</t>
+  </si>
+  <si>
+    <t>14.09.202612</t>
+  </si>
+  <si>
+    <t>14.09.202613</t>
+  </si>
+  <si>
+    <t>14.09.202614</t>
+  </si>
+  <si>
+    <t>14.09.202615</t>
+  </si>
+  <si>
+    <t>14.09.202616</t>
+  </si>
+  <si>
+    <t>14.09.202617</t>
+  </si>
+  <si>
+    <t>14.09.202618</t>
+  </si>
+  <si>
+    <t>14.09.202619</t>
+  </si>
+  <si>
+    <t>14.09.202620</t>
+  </si>
+  <si>
+    <t>14.09.202621</t>
+  </si>
+  <si>
+    <t>14.09.202622</t>
+  </si>
+  <si>
+    <t>14.09.202623</t>
+  </si>
+  <si>
+    <t>14.09.202624</t>
+  </si>
+  <si>
+    <t>15.09.20261</t>
+  </si>
+  <si>
+    <t>15.09.20262</t>
+  </si>
+  <si>
+    <t>15.09.20263</t>
+  </si>
+  <si>
+    <t>15.09.20264</t>
+  </si>
+  <si>
+    <t>15.09.20265</t>
+  </si>
+  <si>
+    <t>15.09.20266</t>
+  </si>
+  <si>
+    <t>15.09.20267</t>
+  </si>
+  <si>
+    <t>15.09.20268</t>
+  </si>
+  <si>
+    <t>15.09.20269</t>
+  </si>
+  <si>
+    <t>15.09.202610</t>
+  </si>
+  <si>
+    <t>15.09.202611</t>
+  </si>
+  <si>
+    <t>15.09.202612</t>
+  </si>
+  <si>
+    <t>15.09.202613</t>
+  </si>
+  <si>
+    <t>15.09.202614</t>
+  </si>
+  <si>
+    <t>15.09.202615</t>
+  </si>
+  <si>
+    <t>15.09.202616</t>
+  </si>
+  <si>
+    <t>15.09.202617</t>
+  </si>
+  <si>
+    <t>15.09.202618</t>
+  </si>
+  <si>
+    <t>15.09.202619</t>
+  </si>
+  <si>
+    <t>15.09.202620</t>
+  </si>
+  <si>
+    <t>15.09.202621</t>
+  </si>
+  <si>
+    <t>15.09.202622</t>
+  </si>
+  <si>
+    <t>15.09.202623</t>
+  </si>
+  <si>
+    <t>15.09.202624</t>
+  </si>
+  <si>
+    <t>16.09.20261</t>
+  </si>
+  <si>
+    <t>16.09.20262</t>
+  </si>
+  <si>
+    <t>16.09.20263</t>
+  </si>
+  <si>
+    <t>16.09.20264</t>
+  </si>
+  <si>
+    <t>16.09.20265</t>
+  </si>
+  <si>
+    <t>16.09.20266</t>
+  </si>
+  <si>
+    <t>16.09.20267</t>
+  </si>
+  <si>
+    <t>16.09.20268</t>
+  </si>
+  <si>
+    <t>16.09.20269</t>
+  </si>
+  <si>
+    <t>16.09.202610</t>
+  </si>
+  <si>
+    <t>16.09.202611</t>
+  </si>
+  <si>
+    <t>16.09.202612</t>
+  </si>
+  <si>
+    <t>16.09.202613</t>
+  </si>
+  <si>
+    <t>16.09.202614</t>
+  </si>
+  <si>
+    <t>16.09.202615</t>
+  </si>
+  <si>
+    <t>16.09.202616</t>
+  </si>
+  <si>
+    <t>16.09.202617</t>
+  </si>
+  <si>
+    <t>16.09.202618</t>
+  </si>
+  <si>
+    <t>16.09.202619</t>
+  </si>
+  <si>
+    <t>16.09.202620</t>
+  </si>
+  <si>
+    <t>16.09.202621</t>
+  </si>
+  <si>
+    <t>16.09.202622</t>
+  </si>
+  <si>
+    <t>16.09.202623</t>
+  </si>
+  <si>
+    <t>16.09.202624</t>
+  </si>
+  <si>
+    <t>17.09.20261</t>
+  </si>
+  <si>
+    <t>17.09.20262</t>
+  </si>
+  <si>
+    <t>17.09.20263</t>
+  </si>
+  <si>
+    <t>17.09.20264</t>
+  </si>
+  <si>
+    <t>17.09.20265</t>
+  </si>
+  <si>
+    <t>17.09.20266</t>
+  </si>
+  <si>
+    <t>17.09.20267</t>
+  </si>
+  <si>
+    <t>17.09.20268</t>
+  </si>
+  <si>
+    <t>17.09.20269</t>
+  </si>
+  <si>
+    <t>17.09.202610</t>
+  </si>
+  <si>
+    <t>17.09.202611</t>
+  </si>
+  <si>
+    <t>17.09.202612</t>
+  </si>
+  <si>
+    <t>17.09.202613</t>
+  </si>
+  <si>
+    <t>17.09.202614</t>
   </si>
 </sst>
 </file>
@@ -913,7 +913,7 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="2">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B2">
         <v>14</v>
@@ -927,7 +927,7 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="2">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B3">
         <v>15</v>
@@ -941,13 +941,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="2">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B4">
         <v>16</v>
       </c>
       <c r="C4">
-        <v>0.962</v>
+        <v>1.131</v>
       </c>
       <c r="D4" t="s">
         <v>6</v>
@@ -955,13 +955,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="2">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B5">
         <v>17</v>
       </c>
       <c r="C5">
-        <v>1.074</v>
+        <v>1.105</v>
       </c>
       <c r="D5" t="s">
         <v>7</v>
@@ -969,13 +969,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="2">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B6">
         <v>18</v>
       </c>
       <c r="C6">
-        <v>0.838</v>
+        <v>0.732</v>
       </c>
       <c r="D6" t="s">
         <v>8</v>
@@ -983,13 +983,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="2">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B7">
         <v>19</v>
       </c>
       <c r="C7">
-        <v>0.485</v>
+        <v>0.292</v>
       </c>
       <c r="D7" t="s">
         <v>9</v>
@@ -997,13 +997,13 @@
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="2">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B8">
         <v>20</v>
       </c>
       <c r="C8">
-        <v>0.199</v>
+        <v>0.034</v>
       </c>
       <c r="D8" t="s">
         <v>10</v>
@@ -1011,7 +1011,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="2">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B9">
         <v>21</v>
@@ -1025,7 +1025,7 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="2">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B10">
         <v>22</v>
@@ -1039,7 +1039,7 @@
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="2">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B11">
         <v>23</v>
@@ -1053,7 +1053,7 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="2">
-        <v>46253</v>
+        <v>46275</v>
       </c>
       <c r="B12">
         <v>24</v>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -1081,7 +1081,7 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B14">
         <v>2</v>
@@ -1095,7 +1095,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -1109,7 +1109,7 @@
     </row>
     <row r="16" spans="1:4">
       <c r="A16" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B16">
         <v>4</v>
@@ -1123,7 +1123,7 @@
     </row>
     <row r="17" spans="1:4">
       <c r="A17" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B17">
         <v>5</v>
@@ -1137,7 +1137,7 @@
     </row>
     <row r="18" spans="1:4">
       <c r="A18" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B18">
         <v>6</v>
@@ -1151,13 +1151,13 @@
     </row>
     <row r="19" spans="1:4">
       <c r="A19" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B19">
         <v>7</v>
       </c>
       <c r="C19">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="D19" t="s">
         <v>21</v>
@@ -1165,13 +1165,13 @@
     </row>
     <row r="20" spans="1:4">
       <c r="A20" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B20">
         <v>8</v>
       </c>
       <c r="C20">
-        <v>0.301</v>
+        <v>0.145</v>
       </c>
       <c r="D20" t="s">
         <v>22</v>
@@ -1179,13 +1179,13 @@
     </row>
     <row r="21" spans="1:4">
       <c r="A21" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B21">
         <v>9</v>
       </c>
       <c r="C21">
-        <v>0.803</v>
+        <v>0.616</v>
       </c>
       <c r="D21" t="s">
         <v>23</v>
@@ -1193,13 +1193,13 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B22">
         <v>10</v>
       </c>
       <c r="C22">
-        <v>0.948</v>
+        <v>1.044</v>
       </c>
       <c r="D22" t="s">
         <v>24</v>
@@ -1207,13 +1207,13 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B23">
         <v>11</v>
       </c>
       <c r="C23">
-        <v>1.548</v>
+        <v>1.266</v>
       </c>
       <c r="D23" t="s">
         <v>25</v>
@@ -1221,13 +1221,13 @@
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B24">
         <v>12</v>
       </c>
       <c r="C24">
-        <v>1.625</v>
+        <v>1.144</v>
       </c>
       <c r="D24" t="s">
         <v>26</v>
@@ -1235,13 +1235,13 @@
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B25">
         <v>13</v>
       </c>
       <c r="C25">
-        <v>1.319</v>
+        <v>1.456</v>
       </c>
       <c r="D25" t="s">
         <v>27</v>
@@ -1249,13 +1249,13 @@
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B26">
         <v>14</v>
       </c>
       <c r="C26">
-        <v>0.949</v>
+        <v>1.191</v>
       </c>
       <c r="D26" t="s">
         <v>28</v>
@@ -1263,13 +1263,13 @@
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B27">
         <v>15</v>
       </c>
       <c r="C27">
-        <v>0.927</v>
+        <v>1.21</v>
       </c>
       <c r="D27" t="s">
         <v>29</v>
@@ -1277,13 +1277,13 @@
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B28">
         <v>16</v>
       </c>
       <c r="C28">
-        <v>0.924</v>
+        <v>0.945</v>
       </c>
       <c r="D28" t="s">
         <v>30</v>
@@ -1291,13 +1291,13 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B29">
         <v>17</v>
       </c>
       <c r="C29">
-        <v>0.927</v>
+        <v>0.96</v>
       </c>
       <c r="D29" t="s">
         <v>31</v>
@@ -1305,13 +1305,13 @@
     </row>
     <row r="30" spans="1:4">
       <c r="A30" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B30">
         <v>18</v>
       </c>
       <c r="C30">
-        <v>0.849</v>
+        <v>0.703</v>
       </c>
       <c r="D30" t="s">
         <v>32</v>
@@ -1319,13 +1319,13 @@
     </row>
     <row r="31" spans="1:4">
       <c r="A31" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B31">
         <v>19</v>
       </c>
       <c r="C31">
-        <v>0.49</v>
+        <v>0.329</v>
       </c>
       <c r="D31" t="s">
         <v>33</v>
@@ -1333,13 +1333,13 @@
     </row>
     <row r="32" spans="1:4">
       <c r="A32" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B32">
         <v>20</v>
       </c>
       <c r="C32">
-        <v>0.17</v>
+        <v>0.034</v>
       </c>
       <c r="D32" t="s">
         <v>34</v>
@@ -1347,7 +1347,7 @@
     </row>
     <row r="33" spans="1:4">
       <c r="A33" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B33">
         <v>21</v>
@@ -1361,7 +1361,7 @@
     </row>
     <row r="34" spans="1:4">
       <c r="A34" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B34">
         <v>22</v>
@@ -1375,7 +1375,7 @@
     </row>
     <row r="35" spans="1:4">
       <c r="A35" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B35">
         <v>23</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="36" spans="1:4">
       <c r="A36" s="2">
-        <v>46254</v>
+        <v>46276</v>
       </c>
       <c r="B36">
         <v>24</v>
@@ -1403,7 +1403,7 @@
     </row>
     <row r="37" spans="1:4">
       <c r="A37" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -1417,7 +1417,7 @@
     </row>
     <row r="38" spans="1:4">
       <c r="A38" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B38">
         <v>2</v>
@@ -1431,7 +1431,7 @@
     </row>
     <row r="39" spans="1:4">
       <c r="A39" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B39">
         <v>3</v>
@@ -1445,7 +1445,7 @@
     </row>
     <row r="40" spans="1:4">
       <c r="A40" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B40">
         <v>4</v>
@@ -1459,7 +1459,7 @@
     </row>
     <row r="41" spans="1:4">
       <c r="A41" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B41">
         <v>5</v>
@@ -1473,7 +1473,7 @@
     </row>
     <row r="42" spans="1:4">
       <c r="A42" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B42">
         <v>6</v>
@@ -1487,13 +1487,13 @@
     </row>
     <row r="43" spans="1:4">
       <c r="A43" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B43">
         <v>7</v>
       </c>
       <c r="C43">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="D43" t="s">
         <v>45</v>
@@ -1501,13 +1501,13 @@
     </row>
     <row r="44" spans="1:4">
       <c r="A44" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B44">
         <v>8</v>
       </c>
       <c r="C44">
-        <v>0.296</v>
+        <v>0.106</v>
       </c>
       <c r="D44" t="s">
         <v>46</v>
@@ -1515,13 +1515,13 @@
     </row>
     <row r="45" spans="1:4">
       <c r="A45" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B45">
         <v>9</v>
       </c>
       <c r="C45">
-        <v>0.789</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="D45" t="s">
         <v>47</v>
@@ -1529,13 +1529,13 @@
     </row>
     <row r="46" spans="1:4">
       <c r="A46" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B46">
         <v>10</v>
       </c>
       <c r="C46">
-        <v>1.249</v>
+        <v>0.805</v>
       </c>
       <c r="D46" t="s">
         <v>48</v>
@@ -1543,13 +1543,13 @@
     </row>
     <row r="47" spans="1:4">
       <c r="A47" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B47">
         <v>11</v>
       </c>
       <c r="C47">
-        <v>1.483</v>
+        <v>1.057</v>
       </c>
       <c r="D47" t="s">
         <v>49</v>
@@ -1557,13 +1557,13 @@
     </row>
     <row r="48" spans="1:4">
       <c r="A48" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B48">
         <v>12</v>
       </c>
       <c r="C48">
-        <v>1.309</v>
+        <v>1.078</v>
       </c>
       <c r="D48" t="s">
         <v>50</v>
@@ -1571,13 +1571,13 @@
     </row>
     <row r="49" spans="1:4">
       <c r="A49" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B49">
         <v>13</v>
       </c>
       <c r="C49">
-        <v>1.377</v>
+        <v>1.393</v>
       </c>
       <c r="D49" t="s">
         <v>51</v>
@@ -1585,13 +1585,13 @@
     </row>
     <row r="50" spans="1:4">
       <c r="A50" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B50">
         <v>14</v>
       </c>
       <c r="C50">
-        <v>1.018</v>
+        <v>1.119</v>
       </c>
       <c r="D50" t="s">
         <v>52</v>
@@ -1599,13 +1599,13 @@
     </row>
     <row r="51" spans="1:4">
       <c r="A51" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B51">
         <v>15</v>
       </c>
       <c r="C51">
-        <v>0.927</v>
+        <v>1.125</v>
       </c>
       <c r="D51" t="s">
         <v>53</v>
@@ -1613,13 +1613,13 @@
     </row>
     <row r="52" spans="1:4">
       <c r="A52" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B52">
         <v>16</v>
       </c>
       <c r="C52">
-        <v>0.924</v>
+        <v>0.967</v>
       </c>
       <c r="D52" t="s">
         <v>54</v>
@@ -1627,13 +1627,13 @@
     </row>
     <row r="53" spans="1:4">
       <c r="A53" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B53">
         <v>17</v>
       </c>
       <c r="C53">
-        <v>0.927</v>
+        <v>0.873</v>
       </c>
       <c r="D53" t="s">
         <v>55</v>
@@ -1641,13 +1641,13 @@
     </row>
     <row r="54" spans="1:4">
       <c r="A54" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B54">
         <v>18</v>
       </c>
       <c r="C54">
-        <v>0.825</v>
+        <v>0.461</v>
       </c>
       <c r="D54" t="s">
         <v>56</v>
@@ -1655,13 +1655,13 @@
     </row>
     <row r="55" spans="1:4">
       <c r="A55" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B55">
         <v>19</v>
       </c>
       <c r="C55">
-        <v>0.49</v>
+        <v>0.145</v>
       </c>
       <c r="D55" t="s">
         <v>57</v>
@@ -1669,13 +1669,13 @@
     </row>
     <row r="56" spans="1:4">
       <c r="A56" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B56">
         <v>20</v>
       </c>
       <c r="C56">
-        <v>0.145</v>
+        <v>0</v>
       </c>
       <c r="D56" t="s">
         <v>58</v>
@@ -1683,7 +1683,7 @@
     </row>
     <row r="57" spans="1:4">
       <c r="A57" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B57">
         <v>21</v>
@@ -1697,7 +1697,7 @@
     </row>
     <row r="58" spans="1:4">
       <c r="A58" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B58">
         <v>22</v>
@@ -1711,7 +1711,7 @@
     </row>
     <row r="59" spans="1:4">
       <c r="A59" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B59">
         <v>23</v>
@@ -1725,7 +1725,7 @@
     </row>
     <row r="60" spans="1:4">
       <c r="A60" s="2">
-        <v>46255</v>
+        <v>46277</v>
       </c>
       <c r="B60">
         <v>24</v>
@@ -1739,7 +1739,7 @@
     </row>
     <row r="61" spans="1:4">
       <c r="A61" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B61">
         <v>1</v>
@@ -1753,7 +1753,7 @@
     </row>
     <row r="62" spans="1:4">
       <c r="A62" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B62">
         <v>2</v>
@@ -1767,7 +1767,7 @@
     </row>
     <row r="63" spans="1:4">
       <c r="A63" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B63">
         <v>3</v>
@@ -1781,7 +1781,7 @@
     </row>
     <row r="64" spans="1:4">
       <c r="A64" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B64">
         <v>4</v>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="65" spans="1:4">
       <c r="A65" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B65">
         <v>5</v>
@@ -1809,7 +1809,7 @@
     </row>
     <row r="66" spans="1:4">
       <c r="A66" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B66">
         <v>6</v>
@@ -1823,13 +1823,13 @@
     </row>
     <row r="67" spans="1:4">
       <c r="A67" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B67">
         <v>7</v>
       </c>
       <c r="C67">
-        <v>0.016</v>
+        <v>0</v>
       </c>
       <c r="D67" t="s">
         <v>69</v>
@@ -1837,13 +1837,13 @@
     </row>
     <row r="68" spans="1:4">
       <c r="A68" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B68">
         <v>8</v>
       </c>
       <c r="C68">
-        <v>0.296</v>
+        <v>0.05</v>
       </c>
       <c r="D68" t="s">
         <v>70</v>
@@ -1851,13 +1851,13 @@
     </row>
     <row r="69" spans="1:4">
       <c r="A69" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B69">
         <v>9</v>
       </c>
       <c r="C69">
-        <v>0.645</v>
+        <v>0.221</v>
       </c>
       <c r="D69" t="s">
         <v>71</v>
@@ -1865,13 +1865,13 @@
     </row>
     <row r="70" spans="1:4">
       <c r="A70" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B70">
         <v>10</v>
       </c>
       <c r="C70">
-        <v>0.967</v>
+        <v>0.576</v>
       </c>
       <c r="D70" t="s">
         <v>72</v>
@@ -1879,13 +1879,13 @@
     </row>
     <row r="71" spans="1:4">
       <c r="A71" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B71">
         <v>11</v>
       </c>
       <c r="C71">
-        <v>1.443</v>
+        <v>0.718</v>
       </c>
       <c r="D71" t="s">
         <v>73</v>
@@ -1893,13 +1893,13 @@
     </row>
     <row r="72" spans="1:4">
       <c r="A72" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B72">
         <v>12</v>
       </c>
       <c r="C72">
-        <v>1.496</v>
+        <v>0.855</v>
       </c>
       <c r="D72" t="s">
         <v>74</v>
@@ -1907,13 +1907,13 @@
     </row>
     <row r="73" spans="1:4">
       <c r="A73" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B73">
         <v>13</v>
       </c>
       <c r="C73">
-        <v>1.375</v>
+        <v>0.848</v>
       </c>
       <c r="D73" t="s">
         <v>75</v>
@@ -1921,13 +1921,13 @@
     </row>
     <row r="74" spans="1:4">
       <c r="A74" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B74">
         <v>14</v>
       </c>
       <c r="C74">
-        <v>0.841</v>
+        <v>0.848</v>
       </c>
       <c r="D74" t="s">
         <v>76</v>
@@ -1935,13 +1935,13 @@
     </row>
     <row r="75" spans="1:4">
       <c r="A75" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B75">
         <v>15</v>
       </c>
       <c r="C75">
-        <v>0.921</v>
+        <v>0.821</v>
       </c>
       <c r="D75" t="s">
         <v>77</v>
@@ -1949,13 +1949,13 @@
     </row>
     <row r="76" spans="1:4">
       <c r="A76" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B76">
         <v>16</v>
       </c>
       <c r="C76">
-        <v>0.918</v>
+        <v>0.631</v>
       </c>
       <c r="D76" t="s">
         <v>78</v>
@@ -1963,13 +1963,13 @@
     </row>
     <row r="77" spans="1:4">
       <c r="A77" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B77">
         <v>17</v>
       </c>
       <c r="C77">
-        <v>0.9330000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="D77" t="s">
         <v>79</v>
@@ -1977,13 +1977,13 @@
     </row>
     <row r="78" spans="1:4">
       <c r="A78" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B78">
         <v>18</v>
       </c>
       <c r="C78">
-        <v>0.825</v>
+        <v>0.291</v>
       </c>
       <c r="D78" t="s">
         <v>80</v>
@@ -1991,13 +1991,13 @@
     </row>
     <row r="79" spans="1:4">
       <c r="A79" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B79">
         <v>19</v>
       </c>
       <c r="C79">
-        <v>0.518</v>
+        <v>0.106</v>
       </c>
       <c r="D79" t="s">
         <v>81</v>
@@ -2005,13 +2005,13 @@
     </row>
     <row r="80" spans="1:4">
       <c r="A80" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B80">
         <v>20</v>
       </c>
       <c r="C80">
-        <v>0.145</v>
+        <v>0</v>
       </c>
       <c r="D80" t="s">
         <v>82</v>
@@ -2019,7 +2019,7 @@
     </row>
     <row r="81" spans="1:4">
       <c r="A81" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B81">
         <v>21</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="82" spans="1:4">
       <c r="A82" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B82">
         <v>22</v>
@@ -2047,7 +2047,7 @@
     </row>
     <row r="83" spans="1:4">
       <c r="A83" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B83">
         <v>23</v>
@@ -2061,7 +2061,7 @@
     </row>
     <row r="84" spans="1:4">
       <c r="A84" s="2">
-        <v>46256</v>
+        <v>46278</v>
       </c>
       <c r="B84">
         <v>24</v>
@@ -2075,7 +2075,7 @@
     </row>
     <row r="85" spans="1:4">
       <c r="A85" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B85">
         <v>1</v>
@@ -2089,7 +2089,7 @@
     </row>
     <row r="86" spans="1:4">
       <c r="A86" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B86">
         <v>2</v>
@@ -2103,7 +2103,7 @@
     </row>
     <row r="87" spans="1:4">
       <c r="A87" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B87">
         <v>3</v>
@@ -2117,7 +2117,7 @@
     </row>
     <row r="88" spans="1:4">
       <c r="A88" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B88">
         <v>4</v>
@@ -2131,7 +2131,7 @@
     </row>
     <row r="89" spans="1:4">
       <c r="A89" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B89">
         <v>5</v>
@@ -2145,7 +2145,7 @@
     </row>
     <row r="90" spans="1:4">
       <c r="A90" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B90">
         <v>6</v>
@@ -2159,13 +2159,13 @@
     </row>
     <row r="91" spans="1:4">
       <c r="A91" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B91">
         <v>7</v>
       </c>
       <c r="C91">
-        <v>0.012</v>
+        <v>0</v>
       </c>
       <c r="D91" t="s">
         <v>93</v>
@@ -2173,13 +2173,13 @@
     </row>
     <row r="92" spans="1:4">
       <c r="A92" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B92">
         <v>8</v>
       </c>
       <c r="C92">
-        <v>0.236</v>
+        <v>0.044</v>
       </c>
       <c r="D92" t="s">
         <v>94</v>
@@ -2187,13 +2187,13 @@
     </row>
     <row r="93" spans="1:4">
       <c r="A93" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B93">
         <v>9</v>
       </c>
       <c r="C93">
-        <v>0.602</v>
+        <v>0.236</v>
       </c>
       <c r="D93" t="s">
         <v>95</v>
@@ -2201,13 +2201,13 @@
     </row>
     <row r="94" spans="1:4">
       <c r="A94" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B94">
         <v>10</v>
       </c>
       <c r="C94">
-        <v>1.013</v>
+        <v>0.623</v>
       </c>
       <c r="D94" t="s">
         <v>96</v>
@@ -2215,13 +2215,13 @@
     </row>
     <row r="95" spans="1:4">
       <c r="A95" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B95">
         <v>11</v>
       </c>
       <c r="C95">
-        <v>1.303</v>
+        <v>0.72</v>
       </c>
       <c r="D95" t="s">
         <v>97</v>
@@ -2229,13 +2229,13 @@
     </row>
     <row r="96" spans="1:4">
       <c r="A96" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B96">
         <v>12</v>
       </c>
       <c r="C96">
-        <v>1.322</v>
+        <v>1.093</v>
       </c>
       <c r="D96" t="s">
         <v>98</v>
@@ -2243,13 +2243,13 @@
     </row>
     <row r="97" spans="1:4">
       <c r="A97" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B97">
         <v>13</v>
       </c>
       <c r="C97">
-        <v>1.502</v>
+        <v>1.03</v>
       </c>
       <c r="D97" t="s">
         <v>99</v>
@@ -2257,13 +2257,13 @@
     </row>
     <row r="98" spans="1:4">
       <c r="A98" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B98">
         <v>14</v>
       </c>
       <c r="C98">
-        <v>0.91</v>
+        <v>0.9419999999999999</v>
       </c>
       <c r="D98" t="s">
         <v>100</v>
@@ -2271,13 +2271,13 @@
     </row>
     <row r="99" spans="1:4">
       <c r="A99" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B99">
         <v>15</v>
       </c>
       <c r="C99">
-        <v>0.771</v>
+        <v>1.079</v>
       </c>
       <c r="D99" t="s">
         <v>101</v>
@@ -2285,13 +2285,13 @@
     </row>
     <row r="100" spans="1:4">
       <c r="A100" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B100">
         <v>16</v>
       </c>
       <c r="C100">
-        <v>0.806</v>
+        <v>1.003</v>
       </c>
       <c r="D100" t="s">
         <v>102</v>
@@ -2299,13 +2299,13 @@
     </row>
     <row r="101" spans="1:4">
       <c r="A101" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B101">
         <v>17</v>
       </c>
       <c r="C101">
-        <v>0.955</v>
+        <v>0.627</v>
       </c>
       <c r="D101" t="s">
         <v>103</v>
@@ -2313,13 +2313,13 @@
     </row>
     <row r="102" spans="1:4">
       <c r="A102" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B102">
         <v>18</v>
       </c>
       <c r="C102">
-        <v>0.664</v>
+        <v>0.46</v>
       </c>
       <c r="D102" t="s">
         <v>104</v>
@@ -2327,13 +2327,13 @@
     </row>
     <row r="103" spans="1:4">
       <c r="A103" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B103">
         <v>19</v>
       </c>
       <c r="C103">
-        <v>0.458</v>
+        <v>0.145</v>
       </c>
       <c r="D103" t="s">
         <v>105</v>
@@ -2341,13 +2341,13 @@
     </row>
     <row r="104" spans="1:4">
       <c r="A104" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B104">
         <v>20</v>
       </c>
       <c r="C104">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="D104" t="s">
         <v>106</v>
@@ -2355,7 +2355,7 @@
     </row>
     <row r="105" spans="1:4">
       <c r="A105" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B105">
         <v>21</v>
@@ -2369,7 +2369,7 @@
     </row>
     <row r="106" spans="1:4">
       <c r="A106" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B106">
         <v>22</v>
@@ -2383,7 +2383,7 @@
     </row>
     <row r="107" spans="1:4">
       <c r="A107" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B107">
         <v>23</v>
@@ -2397,7 +2397,7 @@
     </row>
     <row r="108" spans="1:4">
       <c r="A108" s="2">
-        <v>46257</v>
+        <v>46279</v>
       </c>
       <c r="B108">
         <v>24</v>
@@ -2411,7 +2411,7 @@
     </row>
     <row r="109" spans="1:4">
       <c r="A109" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B109">
         <v>1</v>
@@ -2425,7 +2425,7 @@
     </row>
     <row r="110" spans="1:4">
       <c r="A110" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B110">
         <v>2</v>
@@ -2439,7 +2439,7 @@
     </row>
     <row r="111" spans="1:4">
       <c r="A111" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B111">
         <v>3</v>
@@ -2453,7 +2453,7 @@
     </row>
     <row r="112" spans="1:4">
       <c r="A112" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B112">
         <v>4</v>
@@ -2467,7 +2467,7 @@
     </row>
     <row r="113" spans="1:4">
       <c r="A113" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B113">
         <v>5</v>
@@ -2481,7 +2481,7 @@
     </row>
     <row r="114" spans="1:4">
       <c r="A114" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B114">
         <v>6</v>
@@ -2495,13 +2495,13 @@
     </row>
     <row r="115" spans="1:4">
       <c r="A115" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B115">
         <v>7</v>
       </c>
       <c r="C115">
-        <v>0.011</v>
+        <v>0</v>
       </c>
       <c r="D115" t="s">
         <v>117</v>
@@ -2509,13 +2509,13 @@
     </row>
     <row r="116" spans="1:4">
       <c r="A116" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B116">
         <v>8</v>
       </c>
       <c r="C116">
-        <v>0.221</v>
+        <v>0.073</v>
       </c>
       <c r="D116" t="s">
         <v>118</v>
@@ -2523,13 +2523,13 @@
     </row>
     <row r="117" spans="1:4">
       <c r="A117" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B117">
         <v>9</v>
       </c>
       <c r="C117">
-        <v>0.628</v>
+        <v>0.347</v>
       </c>
       <c r="D117" t="s">
         <v>119</v>
@@ -2537,13 +2537,13 @@
     </row>
     <row r="118" spans="1:4">
       <c r="A118" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B118">
         <v>10</v>
       </c>
       <c r="C118">
-        <v>1.294</v>
+        <v>0.737</v>
       </c>
       <c r="D118" t="s">
         <v>120</v>
@@ -2551,13 +2551,13 @@
     </row>
     <row r="119" spans="1:4">
       <c r="A119" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B119">
         <v>11</v>
       </c>
       <c r="C119">
-        <v>1.528</v>
+        <v>0.9409999999999999</v>
       </c>
       <c r="D119" t="s">
         <v>121</v>
@@ -2565,13 +2565,13 @@
     </row>
     <row r="120" spans="1:4">
       <c r="A120" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B120">
         <v>12</v>
       </c>
       <c r="C120">
-        <v>1.485</v>
+        <v>1.038</v>
       </c>
       <c r="D120" t="s">
         <v>122</v>
@@ -2579,13 +2579,13 @@
     </row>
     <row r="121" spans="1:4">
       <c r="A121" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B121">
         <v>13</v>
       </c>
       <c r="C121">
-        <v>1.338</v>
+        <v>1.063</v>
       </c>
       <c r="D121" t="s">
         <v>123</v>
@@ -2593,13 +2593,13 @@
     </row>
     <row r="122" spans="1:4">
       <c r="A122" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B122">
         <v>14</v>
       </c>
       <c r="C122">
-        <v>0.862</v>
+        <v>1.152</v>
       </c>
       <c r="D122" t="s">
         <v>124</v>
@@ -2607,13 +2607,13 @@
     </row>
     <row r="123" spans="1:4">
       <c r="A123" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B123">
         <v>15</v>
       </c>
       <c r="C123">
-        <v>1.005</v>
+        <v>1.224</v>
       </c>
       <c r="D123" t="s">
         <v>125</v>
@@ -2621,13 +2621,13 @@
     </row>
     <row r="124" spans="1:4">
       <c r="A124" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B124">
         <v>16</v>
       </c>
       <c r="C124">
-        <v>0.953</v>
+        <v>1.101</v>
       </c>
       <c r="D124" t="s">
         <v>126</v>
@@ -2635,13 +2635,13 @@
     </row>
     <row r="125" spans="1:4">
       <c r="A125" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B125">
         <v>17</v>
       </c>
       <c r="C125">
-        <v>0.996</v>
+        <v>0.92</v>
       </c>
       <c r="D125" t="s">
         <v>127</v>
@@ -2649,13 +2649,13 @@
     </row>
     <row r="126" spans="1:4">
       <c r="A126" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B126">
         <v>18</v>
       </c>
       <c r="C126">
-        <v>0.79</v>
+        <v>0.553</v>
       </c>
       <c r="D126" t="s">
         <v>128</v>
@@ -2663,13 +2663,13 @@
     </row>
     <row r="127" spans="1:4">
       <c r="A127" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B127">
         <v>19</v>
       </c>
       <c r="C127">
-        <v>0.434</v>
+        <v>0.145</v>
       </c>
       <c r="D127" t="s">
         <v>129</v>
@@ -2677,13 +2677,13 @@
     </row>
     <row r="128" spans="1:4">
       <c r="A128" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B128">
         <v>20</v>
       </c>
       <c r="C128">
-        <v>0.145</v>
+        <v>0</v>
       </c>
       <c r="D128" t="s">
         <v>130</v>
@@ -2691,7 +2691,7 @@
     </row>
     <row r="129" spans="1:4">
       <c r="A129" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B129">
         <v>21</v>
@@ -2705,7 +2705,7 @@
     </row>
     <row r="130" spans="1:4">
       <c r="A130" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B130">
         <v>22</v>
@@ -2719,7 +2719,7 @@
     </row>
     <row r="131" spans="1:4">
       <c r="A131" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B131">
         <v>23</v>
@@ -2733,7 +2733,7 @@
     </row>
     <row r="132" spans="1:4">
       <c r="A132" s="2">
-        <v>46258</v>
+        <v>46280</v>
       </c>
       <c r="B132">
         <v>24</v>
@@ -2747,7 +2747,7 @@
     </row>
     <row r="133" spans="1:4">
       <c r="A133" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B133">
         <v>1</v>
@@ -2761,7 +2761,7 @@
     </row>
     <row r="134" spans="1:4">
       <c r="A134" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B134">
         <v>2</v>
@@ -2775,7 +2775,7 @@
     </row>
     <row r="135" spans="1:4">
       <c r="A135" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B135">
         <v>3</v>
@@ -2789,7 +2789,7 @@
     </row>
     <row r="136" spans="1:4">
       <c r="A136" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B136">
         <v>4</v>
@@ -2803,7 +2803,7 @@
     </row>
     <row r="137" spans="1:4">
       <c r="A137" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B137">
         <v>5</v>
@@ -2817,7 +2817,7 @@
     </row>
     <row r="138" spans="1:4">
       <c r="A138" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B138">
         <v>6</v>
@@ -2831,7 +2831,7 @@
     </row>
     <row r="139" spans="1:4">
       <c r="A139" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B139">
         <v>7</v>
@@ -2845,13 +2845,13 @@
     </row>
     <row r="140" spans="1:4">
       <c r="A140" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B140">
         <v>8</v>
       </c>
       <c r="C140">
-        <v>0.221</v>
+        <v>0.106</v>
       </c>
       <c r="D140" t="s">
         <v>142</v>
@@ -2859,13 +2859,13 @@
     </row>
     <row r="141" spans="1:4">
       <c r="A141" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B141">
         <v>9</v>
       </c>
       <c r="C141">
-        <v>0.647</v>
+        <v>0.589</v>
       </c>
       <c r="D141" t="s">
         <v>143</v>
@@ -2873,13 +2873,13 @@
     </row>
     <row r="142" spans="1:4">
       <c r="A142" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B142">
         <v>10</v>
       </c>
       <c r="C142">
-        <v>0.863</v>
+        <v>0.96</v>
       </c>
       <c r="D142" t="s">
         <v>144</v>
@@ -2887,13 +2887,13 @@
     </row>
     <row r="143" spans="1:4">
       <c r="A143" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B143">
         <v>11</v>
       </c>
       <c r="C143">
-        <v>0.8169999999999999</v>
+        <v>1.302</v>
       </c>
       <c r="D143" t="s">
         <v>145</v>
@@ -2901,13 +2901,13 @@
     </row>
     <row r="144" spans="1:4">
       <c r="A144" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B144">
         <v>12</v>
       </c>
       <c r="C144">
-        <v>1.463</v>
+        <v>1.324</v>
       </c>
       <c r="D144" t="s">
         <v>146</v>
@@ -2915,13 +2915,13 @@
     </row>
     <row r="145" spans="1:4">
       <c r="A145" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B145">
         <v>13</v>
       </c>
       <c r="C145">
-        <v>1.502</v>
+        <v>0.801</v>
       </c>
       <c r="D145" t="s">
         <v>147</v>
@@ -2929,13 +2929,13 @@
     </row>
     <row r="146" spans="1:4">
       <c r="A146" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B146">
         <v>14</v>
       </c>
       <c r="C146">
-        <v>1.155</v>
+        <v>0.792</v>
       </c>
       <c r="D146" t="s">
         <v>148</v>
@@ -2943,7 +2943,7 @@
     </row>
     <row r="147" spans="1:4">
       <c r="A147" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B147">
         <v>15</v>
@@ -2957,13 +2957,13 @@
     </row>
     <row r="148" spans="1:4">
       <c r="A148" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B148">
         <v>16</v>
       </c>
       <c r="C148">
-        <v>0.961</v>
+        <v>0.949</v>
       </c>
       <c r="D148" t="s">
         <v>150</v>
@@ -2971,13 +2971,13 @@
     </row>
     <row r="149" spans="1:4">
       <c r="A149" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B149">
         <v>17</v>
       </c>
       <c r="C149">
-        <v>0.947</v>
+        <v>1.006</v>
       </c>
       <c r="D149" t="s">
         <v>151</v>
@@ -2985,13 +2985,13 @@
     </row>
     <row r="150" spans="1:4">
       <c r="A150" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B150">
         <v>18</v>
       </c>
       <c r="C150">
-        <v>0.761</v>
+        <v>0.626</v>
       </c>
       <c r="D150" t="s">
         <v>152</v>
@@ -2999,13 +2999,13 @@
     </row>
     <row r="151" spans="1:4">
       <c r="A151" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B151">
         <v>19</v>
       </c>
       <c r="C151">
-        <v>0.469</v>
+        <v>0.232</v>
       </c>
       <c r="D151" t="s">
         <v>153</v>
@@ -3013,13 +3013,13 @@
     </row>
     <row r="152" spans="1:4">
       <c r="A152" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B152">
         <v>20</v>
       </c>
       <c r="C152">
-        <v>0.106</v>
+        <v>0</v>
       </c>
       <c r="D152" t="s">
         <v>154</v>
@@ -3027,7 +3027,7 @@
     </row>
     <row r="153" spans="1:4">
       <c r="A153" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B153">
         <v>21</v>
@@ -3041,7 +3041,7 @@
     </row>
     <row r="154" spans="1:4">
       <c r="A154" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B154">
         <v>22</v>
@@ -3055,7 +3055,7 @@
     </row>
     <row r="155" spans="1:4">
       <c r="A155" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B155">
         <v>23</v>
@@ -3069,7 +3069,7 @@
     </row>
     <row r="156" spans="1:4">
       <c r="A156" s="2">
-        <v>46259</v>
+        <v>46281</v>
       </c>
       <c r="B156">
         <v>24</v>
@@ -3083,7 +3083,7 @@
     </row>
     <row r="157" spans="1:4">
       <c r="A157" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B157">
         <v>1</v>
@@ -3097,7 +3097,7 @@
     </row>
     <row r="158" spans="1:4">
       <c r="A158" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B158">
         <v>2</v>
@@ -3111,7 +3111,7 @@
     </row>
     <row r="159" spans="1:4">
       <c r="A159" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B159">
         <v>3</v>
@@ -3125,7 +3125,7 @@
     </row>
     <row r="160" spans="1:4">
       <c r="A160" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B160">
         <v>4</v>
@@ -3139,7 +3139,7 @@
     </row>
     <row r="161" spans="1:4">
       <c r="A161" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B161">
         <v>5</v>
@@ -3153,7 +3153,7 @@
     </row>
     <row r="162" spans="1:4">
       <c r="A162" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B162">
         <v>6</v>
@@ -3167,7 +3167,7 @@
     </row>
     <row r="163" spans="1:4">
       <c r="A163" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B163">
         <v>7</v>
@@ -3181,13 +3181,13 @@
     </row>
     <row r="164" spans="1:4">
       <c r="A164" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B164">
         <v>8</v>
       </c>
       <c r="C164">
-        <v>0.168</v>
+        <v>0.106</v>
       </c>
       <c r="D164" t="s">
         <v>166</v>
@@ -3195,13 +3195,13 @@
     </row>
     <row r="165" spans="1:4">
       <c r="A165" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B165">
         <v>9</v>
       </c>
       <c r="C165">
-        <v>0.529</v>
+        <v>0.656</v>
       </c>
       <c r="D165" t="s">
         <v>167</v>
@@ -3209,13 +3209,13 @@
     </row>
     <row r="166" spans="1:4">
       <c r="A166" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B166">
         <v>10</v>
       </c>
       <c r="C166">
-        <v>0.626</v>
+        <v>1.058</v>
       </c>
       <c r="D166" t="s">
         <v>168</v>
@@ -3223,13 +3223,13 @@
     </row>
     <row r="167" spans="1:4">
       <c r="A167" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B167">
         <v>11</v>
       </c>
       <c r="C167">
-        <v>1.017</v>
+        <v>1.149</v>
       </c>
       <c r="D167" t="s">
         <v>169</v>
@@ -3237,13 +3237,13 @@
     </row>
     <row r="168" spans="1:4">
       <c r="A168" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B168">
         <v>12</v>
       </c>
       <c r="C168">
-        <v>1.307</v>
+        <v>0.79</v>
       </c>
       <c r="D168" t="s">
         <v>170</v>
@@ -3251,13 +3251,13 @@
     </row>
     <row r="169" spans="1:4">
       <c r="A169" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B169">
         <v>13</v>
       </c>
       <c r="C169">
-        <v>1.431</v>
+        <v>0.8129999999999999</v>
       </c>
       <c r="D169" t="s">
         <v>171</v>
@@ -3265,13 +3265,13 @@
     </row>
     <row r="170" spans="1:4">
       <c r="A170" s="2">
-        <v>46260</v>
+        <v>46282</v>
       </c>
       <c r="B170">
         <v>14</v>
       </c>
       <c r="C170">
-        <v>1.078</v>
+        <v>0.873</v>
       </c>
       <c r="D170" t="s">
         <v>172</v>
